--- a/CATI/saved_states/NABIL_future_30_day_forecast.xlsx
+++ b/CATI/saved_states/NABIL_future_30_day_forecast.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,392 +451,93 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>45938</v>
+        <v>46003</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.5714081285771611</v>
+        <v>0.3606313031927393</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>45939</v>
+        <v>46006</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.5711269543859615</v>
+        <v>0.3606313031927393</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>45940</v>
+        <v>46007</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.5789961472963068</v>
+        <v>0.3606313031927393</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>45943</v>
+        <v>46008</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.5833010320224723</v>
+        <v>0.3606313031927393</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>45944</v>
+        <v>46009</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.5879504372194981</v>
+        <v>0.3606313031927393</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>45945</v>
+        <v>46010</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.590979417611557</v>
+        <v>0.3606313031927393</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>45946</v>
+        <v>46013</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.5945961374357285</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="n">
-        <v>45947</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>0.5911753421389493</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="n">
-        <v>45950</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>0.5975807797608076</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="n">
-        <v>45951</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>0.6008740195909528</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="n">
-        <v>45952</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>0.6022074941648256</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="n">
-        <v>45953</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>0.6014530421058046</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="n">
-        <v>45954</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>0.5959883727740045</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="n">
-        <v>45957</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>0.5994333289469029</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="n">
-        <v>45958</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>0.6003160695788545</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="n">
-        <v>45959</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>0.6064931255528676</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="n">
-        <v>45960</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>0.6004546891820318</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="n">
-        <v>45961</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>0.5962182832485803</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="n">
-        <v>45964</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>0.5979863728149064</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="n">
-        <v>45965</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>0.6013956810328778</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="n">
-        <v>45966</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>0.60133975110494</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="n">
-        <v>45967</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>0.5978810480428727</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="n">
-        <v>45968</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>0.5939538514825187</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="n">
-        <v>45971</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>0.5828670133827567</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="n">
-        <v>45972</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>0.5758080406683472</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="n">
-        <v>45973</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>0.5761492939507517</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="n">
-        <v>45974</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>0.5756633828189088</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="n">
-        <v>45975</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>0.5755761916845268</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="n">
-        <v>45978</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>0.5757183124037188</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="n">
-        <v>45979</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>0.5759209940936281</v>
+        <v>0.3606312833245244</v>
       </c>
     </row>
   </sheetData>

--- a/CATI/saved_states/NABIL_future_30_day_forecast.xlsx
+++ b/CATI/saved_states/NABIL_future_30_day_forecast.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,11 +443,6 @@
           <t>Signal</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Score</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
@@ -458,9 +453,6 @@
           <t>SELL</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>0.3606313031927393</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -471,9 +463,6 @@
           <t>SELL</t>
         </is>
       </c>
-      <c r="C3" t="n">
-        <v>0.3606313031927393</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -484,9 +473,6 @@
           <t>SELL</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>0.3606313031927393</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -497,9 +483,6 @@
           <t>SELL</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>0.3606313031927393</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -510,9 +493,6 @@
           <t>SELL</t>
         </is>
       </c>
-      <c r="C6" t="n">
-        <v>0.3606313031927393</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -523,9 +503,6 @@
           <t>SELL</t>
         </is>
       </c>
-      <c r="C7" t="n">
-        <v>0.3606313031927393</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -535,9 +512,6 @@
         <is>
           <t>SELL</t>
         </is>
-      </c>
-      <c r="C8" t="n">
-        <v>0.3606312833245244</v>
       </c>
     </row>
   </sheetData>

--- a/CATI/saved_states/NABIL_future_30_day_forecast.xlsx
+++ b/CATI/saved_states/NABIL_future_30_day_forecast.xlsx
@@ -1,40 +1,68 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Home\BE\projects\stock_market_prediction\CATI\saved_states\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01CE5A51-2327-430B-92AD-98C6139376EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Forecast" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Forecast" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="4">
+  <si>
+    <t>Forecast_Date</t>
+  </si>
+  <si>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>SELL</t>
+  </si>
+  <si>
+    <t>BUY</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -49,94 +77,44 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -424,94 +402,75 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="18.5546875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Forecast_Date</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Signal</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="n">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="2">
         <v>46003</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="2">
         <v>46006</v>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="B3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
         <v>46007</v>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="B4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="2">
         <v>46008</v>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="B5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="2">
         <v>46009</v>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="B6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="2">
         <v>46010</v>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="B7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="2">
         <v>46013</v>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
+      <c r="B8" t="s">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
